--- a/ig/DM-OCTOBRE-2026/ValueSet-jdv-mesure-lentille-prescrite-cisis.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-jdv-mesure-lentille-prescrite-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260916095452</t>
+    <t>20260928134048</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:54:52+01:00</t>
+    <t>2026-09-28T13:40:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
